--- a/forecasting.xlsx
+++ b/forecasting.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:AE61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,72 +437,142 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Condizioni Pagamento</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Antecedenti 2025</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Gennaio</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Febbraio</t>
+          <t>Gennaio 2025</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Febbraio 2025</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Aprile</t>
+          <t>Marzo 2025</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Maggio</t>
+          <t>Aprile 2025</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Giugno</t>
+          <t>Maggio 2025</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Luglio</t>
+          <t>Giugno 2025</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Luglio 2025</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Settembre</t>
+          <t>Agosto 2025</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Ottobre</t>
+          <t>Settembre 2025</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Novembre</t>
+          <t>Ottobre 2025</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Dicembre</t>
+          <t>Novembre 2025</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Totale Anno</t>
+          <t>Dicembre 2025</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Totale 2025</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Gennaio 2026</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Febbraio 2026</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Marzo 2026</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Aprile 2026</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Maggio 2026</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Giugno 2026</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Luglio 2026</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Agosto 2026</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Settembre 2026</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Ottobre 2026</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Novembre 2026</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Dicembre 2026</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Totale 2026</t>
         </is>
       </c>
     </row>
@@ -517,9 +587,15 @@
           <t>F0002337</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>54.10.0260</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BB 60GG FM</t>
+        </is>
       </c>
       <c r="E2" s="1" t="n">
         <v>0</v>
@@ -528,20 +604,20 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="1" t="n">
         <v>0</v>
       </c>
@@ -558,7 +634,49 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="n">
         <v>1800</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -572,9 +690,15 @@
           <t>F0002795</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="1" t="n">
-        <v>0</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>50% ANTICIPATO - 50% A MERCE PRONTA</t>
+        </is>
       </c>
       <c r="E3" s="1" t="n">
         <v>0</v>
@@ -601,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>16318.56959999999</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>0</v>
@@ -610,30 +734,74 @@
         <v>0</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0</v>
+        <v>13434.07</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>16318.56959999999</v>
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>13434.07</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALBASCREEN SRL</t>
+          <t>ACTION TECHNOLOGY ITALIA SPA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F0007038</t>
+          <t>F0001292</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>54.10.0057</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0504</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RIBA 30GG FM + 5 GG</t>
+        </is>
       </c>
       <c r="E4" s="1" t="n">
         <v>0</v>
@@ -642,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>67.8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
@@ -672,27 +840,71 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>94.8</v>
+        <v>562.8</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>562.8</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALCE S.A.S. DI CAVAZZINI F.N. &amp; C</t>
+          <t>ALASCOM SRL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F0000081</t>
+          <t>F0003384</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.10.0503</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BB 60GG DF FM</t>
+        </is>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
@@ -719,35 +931,83 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>2306.4</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>3868.8</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>2845.8</v>
+        <v>0</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>1841.4</v>
+        <v>950</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>10862.4</v>
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>950</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APE AUTOMAZIONE S.R.L.</t>
+          <t>ALBASCREEN SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F0002166</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
+          <t>F0007038</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>54.10.0057</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RB 30/60/90 GG FM + 10</t>
+        </is>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
@@ -759,13 +1019,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>806.04</v>
+        <v>18</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0</v>
@@ -786,27 +1046,71 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>806.04</v>
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APTAR ITALIA SPA</t>
+          <t>ALBERTIN ALCIDE &amp; FIGLI S.N.C.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F0000175</t>
+          <t>F0002692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.10.0504</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0030, 54.10.0057</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BB 60GG FM IL 10</t>
+        </is>
       </c>
       <c r="E7" s="1" t="n">
         <v>0</v>
@@ -833,39 +1137,83 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>23538.52</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>13866.58</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>22869</v>
+        <v>0</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>22869</v>
+        <v>28</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>83143.10000000001</v>
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARSMETALLO S.R.L.</t>
+          <t>ALCE S.A.S. DI CAVAZZINI F.N. &amp; C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F0010242</t>
+          <t>F0000081</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54.10.0503</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0501, 50.10.0503, 50.20.0501</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 GG FM</t>
+        </is>
       </c>
       <c r="E8" s="1" t="n">
         <v>0</v>
@@ -886,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0</v>
@@ -895,36 +1243,80 @@
         <v>0</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>27862.02</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>10375</v>
+        <v>0</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0</v>
+        <v>1221.9</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>38687.02</v>
+        <v>4352.4</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>5574.3</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>2176.2</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>2176.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BETLEMME DI PENG FUTANG</t>
+          <t>APE AUTOMAZIONE S.R.L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F0003144</t>
+          <t>F0002166</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>54.10.0504</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>81.90000000000001</v>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RIBA 30/60 GG DF. F.M. + 5 GG.</t>
+        </is>
       </c>
       <c r="E9" s="1" t="n">
         <v>0</v>
@@ -945,41 +1337,89 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0</v>
+        <v>806.04</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>6322.92</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>18779.6</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>26696.42</v>
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>806.04</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRESCIA STAMPI SRL</t>
+          <t>APTAR ITALIA SPA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F0002921</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" s="1" t="n">
-        <v>4400</v>
+          <t>F0000175</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>50.10.0504</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ANTICIPATO ANTE SPEDIZIONE SCONTO 1%</t>
+        </is>
       </c>
       <c r="E10" s="1" t="n">
         <v>0</v>
@@ -1009,36 +1449,80 @@
         <v>0</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0</v>
+        <v>12760</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0</v>
+        <v>10672.2</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0</v>
+        <v>22869</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>4400</v>
+        <v>33541.2</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>79842.39999999999</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>1600.7</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>1600.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CGT GUBERTI SPA</t>
+          <t>ARSMETALLO S.R.L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F0002329</t>
+          <t>F0010242</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>50.10.0301</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0100, 54.10.0503</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RB 30/60/90 GG FM + 5 GG</t>
+        </is>
       </c>
       <c r="E11" s="1" t="n">
         <v>0</v>
@@ -1062,42 +1546,86 @@
         <v>0</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>3492.5</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>2681.25</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0</v>
+        <v>38237.02</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>6173.75</v>
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>38687.02</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COLORFLEX SRL</t>
+          <t>BETLEMME DI PENG FUTANG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F0001656</t>
+          <t>F0003144</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50.10.0302</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>47.39</v>
+          <t>54.10.0504</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BB30/60/90/120 GG FM+10</t>
+        </is>
       </c>
       <c r="E12" s="1" t="n">
         <v>0</v>
@@ -1133,26 +1661,74 @@
         <v>0</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0</v>
+        <v>4365.440000000001</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>47.39</v>
+        <v>8286.799999999999</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>12652.24</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>1068.9</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>1068.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COSMETIXPACK LIMITED</t>
+          <t>CGT GUBERTI SPA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F0003409</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" s="1" t="n">
-        <v>0</v>
+          <t>F0002329</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>50.10.0301</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RB 30/60/90 GG FM + 10</t>
+        </is>
       </c>
       <c r="E13" s="1" t="n">
         <v>0</v>
@@ -1170,48 +1746,92 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>14725.27</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>197.8</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>263.74</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>6428.58</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0</v>
+        <v>3931.25</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>21615.39</v>
+        <v>3217.5</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>9398.75</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D.P.S. D'ASIO PACKAGING SOLUTION DI D'ASIO LUIGI</t>
+          <t>COSMETIXPACK LIMITED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F0007054</t>
+          <t>F0003409</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>54.10.0504</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PAGAMENTO CONCORDATO</t>
+        </is>
       </c>
       <c r="E14" s="1" t="n">
         <v>0</v>
@@ -1229,44 +1849,92 @@
         <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>93.583</v>
+        <v>14725.27</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0</v>
+        <v>197.8</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>2982.83</v>
+        <v>263.74</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>2719.74</v>
+        <v>6428.58</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>2355.92</v>
+        <v>0</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>1987.78</v>
+        <v>1010.99</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>10313.853</v>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>22626.37999999999</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>29454.67</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>29454.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DECOR  GLASS S.R.L.</t>
+          <t>COSTER TECNOLOGIE SPECIALI SPA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>00099862</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="1" t="n">
-        <v>4</v>
+          <t>F0000012</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>50.10.0504</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BB 60GG FM</t>
+        </is>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -1302,30 +1970,74 @@
         <v>0</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>9090</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>9090</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DETER S.R.L.</t>
+          <t>D.P.S. D'ASIO PACKAGING SOLUTION DI D'ASIO LUIGI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>F0001745</t>
+          <t>F0007054</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52.10.0011</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>108.47</v>
+          <t>54.10.0503</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM +10</t>
+        </is>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -1346,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0</v>
+        <v>93.583</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>0</v>
@@ -1358,33 +2070,77 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0</v>
+        <v>851.39</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0</v>
+        <v>2318.92</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>108.47</v>
+        <v>2672.03</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>6109.923</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>695.1</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>695.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ELABORA SRL</t>
+          <t>DEKORGLASS DZIALDOWO S.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>F0001806</t>
+          <t>F0001964</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>54.10.0004</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAGAMENTO ANTICIPATO</t>
+        </is>
       </c>
       <c r="E17" s="1" t="n">
         <v>0</v>
@@ -1405,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
@@ -1420,26 +2176,74 @@
         <v>0</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0</v>
+        <v>4750</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>1200</v>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>4750</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMME PACKAGING SRL</t>
+          <t>DEMAFLEX  S.A.S. DI DE GAETANO MARCO &amp; C.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F0002891</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
+          <t>F0002653</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BB 30GG FM</t>
+        </is>
       </c>
       <c r="E18" s="1" t="n">
         <v>0</v>
@@ -1460,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>193.5</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>0</v>
@@ -1472,29 +2276,77 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0</v>
+        <v>62.4</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>193.5</v>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EMMEPLAST SRL</t>
+          <t>DUE EMME AUTOMAZIONE SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>F0010266</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" s="1" t="n">
-        <v>0</v>
+          <t>F0001725</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>54.10.0504</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BB 60GG FM IL 10</t>
+        </is>
       </c>
       <c r="E19" s="1" t="n">
         <v>0</v>
@@ -1524,32 +2376,80 @@
         <v>0</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>14830</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>15714</v>
+        <v>177.5</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>30544</v>
+        <v>0</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETTORE SCAGLIA SRL</t>
+          <t>ELABORA SRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F0007032</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="1" t="n">
-        <v>1050</v>
+          <t>F0001806</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>54.10.0004, 54.10.0005</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RIBA 60GG FM</t>
+        </is>
       </c>
       <c r="E20" s="1" t="n">
         <v>0</v>
@@ -1573,13 +2473,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>0</v>
@@ -1588,27 +2488,71 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>1650</v>
+        <v>0</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EUROCOLOR SRL</t>
+          <t>EMME PACKAGING SRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>F0000686</t>
+          <t>F0002891</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>50.10.0301</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0101, 50.20.0502</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RIBA 30GG FM + 10 GG</t>
+        </is>
       </c>
       <c r="E21" s="1" t="n">
         <v>0</v>
@@ -1617,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
@@ -1632,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0</v>
+        <v>193.5</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>0</v>
@@ -1647,39 +2591,83 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>7200</v>
+        <v>0</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FI.VER.S. S.N.C.</t>
+          <t>EMMEPLAST SRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F0002765</t>
+          <t>F0010266</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>54.10.0501</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>150</v>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RIBA 30/60GG FM</t>
+        </is>
       </c>
       <c r="E22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>135.8685</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1975</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>0</v>
@@ -1703,32 +2691,80 @@
         <v>0</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0</v>
+        <v>15714</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>2260.8685</v>
+        <v>0</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>15714</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FISMET SERVICE</t>
+          <t>ETTORE SCAGLIA SRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F0007048</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" s="1" t="n">
-        <v>0</v>
+          <t>F0007032</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>50.10.0013, 50.10.0503</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BB 90GG DF FM</t>
+        </is>
       </c>
       <c r="E23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>0</v>
@@ -1755,33 +2791,77 @@
         <v>0</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GP IMBALLAGGI S.A.S. DI PINI SERGIO</t>
+          <t>EUROCOLOR SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F0002327</t>
+          <t>F0000686</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>50.20.0503</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0301</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RIBA 90GG FM</t>
+        </is>
       </c>
       <c r="E24" s="1" t="n">
         <v>0</v>
@@ -1793,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>0</v>
@@ -1808,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>0</v>
@@ -1817,30 +2897,74 @@
         <v>0</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0</v>
+        <v>687.5</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>428</v>
+        <v>0</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>7887.5</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HEINZ GLAS POLSKA SP. Z.O.O</t>
+          <t>FI.VER.S. S.N.C.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F0001662</t>
+          <t>F0002765</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50.10.0701</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0502, 54.10.0503</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BB 60/90/120 GG FM</t>
+        </is>
       </c>
       <c r="E25" s="1" t="n">
         <v>0</v>
@@ -1849,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0</v>
+        <v>135.8685</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0</v>
+        <v>1975</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>0</v>
@@ -1870,36 +2994,80 @@
         <v>0</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>5806.87</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>10348.86</v>
+        <v>0</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>16155.73</v>
+        <v>0</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>2110.8685</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IGIENPUL S.R.L.</t>
+          <t>FISMET SERVICE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F0002696</t>
+          <t>F0007048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>52.10.0011</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>226.4</v>
+          <t>54.10.0503</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RIBA 60GG FM</t>
+        </is>
       </c>
       <c r="E26" s="1" t="n">
         <v>0</v>
@@ -1908,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0</v>
@@ -1938,27 +3106,71 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>226.4</v>
+        <v>0</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IMAS GRAFICA SRL</t>
+          <t>GIMA S.N.C. di Nespoli e Citterio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>F0001648</t>
+          <t>F0000694</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.10.0202</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>69.7</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E27" s="1" t="n">
         <v>0</v>
@@ -1994,26 +3206,74 @@
         <v>0</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>0</v>
+        <v>5720.179999999999</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>69.7</v>
+        <v>40812.41</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>46532.59</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>262.66</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1" t="n">
+        <v>262.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT IMPRESA SRL</t>
+          <t>GP IMBALLAGGI S.A.S. DI PINI SERGIO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F0003340</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="1" t="n">
-        <v>0</v>
+          <t>F0002327</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>50.10.0103, 50.20.0503</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BB 60GG FM</t>
+        </is>
       </c>
       <c r="E28" s="1" t="n">
         <v>0</v>
@@ -2022,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0</v>
@@ -2043,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>0</v>
@@ -2052,30 +3312,74 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>776</v>
+        <v>0</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>428</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ITALPRINT S.N.C. DI P.DE CARO &amp; C.</t>
+          <t>HEINZ GLAS POLSKA SP. Z.O.O</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>F0000165</t>
+          <t>F0001662</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>54.10.0503</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>30% ORDINE - 70% MERCE PRONTA</t>
+        </is>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0</v>
@@ -2084,50 +3388,98 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>8803.109999999999</v>
+        <v>0</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>0</v>
+        <v>5806.87</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>0</v>
+        <v>10348.86</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>11261.11</v>
+        <v>0</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>16155.73</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LA MORONA SRL</t>
+          <t>IGIENPUL S.R.L.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>F0002556</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="1" t="n">
-        <v>0</v>
+          <t>F0002696</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>50.10.0210, 52.10.0010, 52.10.0011</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RIBA 30GG FM + 5 GG</t>
+        </is>
       </c>
       <c r="E30" s="1" t="n">
         <v>0</v>
@@ -2154,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>49.8</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>0</v>
@@ -2163,30 +3515,74 @@
         <v>0</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>49.8</v>
+        <v>0</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LA TRASMISSIONE SRL</t>
+          <t>IT IMPRESA SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F0002594</t>
+          <t>F0003340</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.10.0202</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0004, 54.10.0005</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E31" s="1" t="n">
         <v>0</v>
@@ -2195,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>228.9</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0</v>
@@ -2225,27 +3621,71 @@
         <v>0</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>228.9</v>
+        <v>0</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>776</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LA TRASPARENTE SAS DI GIOVANNI MUNAFÒ &amp; C. SAS</t>
+          <t>ITALPRINT S.N.C. DI P.DE CARO &amp; C.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F0000490</t>
+          <t>F0000165</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>50.20.0502</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0503</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BB 30/60/90/120 GG FM</t>
+        </is>
       </c>
       <c r="E32" s="1" t="n">
         <v>0</v>
@@ -2260,102 +3700,198 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>1560</v>
+        <v>108</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>0</v>
+        <v>7118.98</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>0</v>
+        <v>1669.57</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>1560</v>
+        <v>2315.64</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>12272.19</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>1979.82</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1" t="n">
+        <v>1979.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LORETELLI DANIELA SRL</t>
+          <t>LA TRASMISSIONE SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>F003230</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" s="1" t="n">
-        <v>0</v>
+          <t>F0002594</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RIBA 60GG FM + 5 GG</t>
+        </is>
       </c>
       <c r="E33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>6630</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0</v>
+        <v>228.9</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>1881.25</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>6906.5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>17279.453</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>35397.03</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>7570</v>
+        <v>0</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>79219.23299999998</v>
+        <v>0</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>M5 BIADESIVI SRL</t>
+          <t>LA TRASPARENTE SAS DI GIOVANNI MUNAFÒ &amp; C. SAS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>F003259</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" s="1" t="n">
-        <v>0</v>
+          <t>F0000490</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>50.10.0101, 50.20.0501, 50.20.0502</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BB 30/60 GG FM + 10</t>
+        </is>
       </c>
       <c r="E34" s="1" t="n">
         <v>0</v>
@@ -2376,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>92.48</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0</v>
@@ -2385,36 +3921,80 @@
         <v>0</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>92.48</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>0</v>
+        <v>4824</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>184.96</v>
+        <v>1632</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>6456</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MANUPLAST SRL</t>
+          <t>LORETELLI DANIELA SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>F0000666</t>
+          <t>F003230</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>54.10.0502</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0010, 50.10.0013, 50.20.0503, 54.10.0501, 54.10.0502, 54.10.0503</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM +10</t>
+        </is>
       </c>
       <c r="E35" s="1" t="n">
         <v>0</v>
@@ -2423,57 +4003,101 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0</v>
+        <v>6630</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>60</v>
+        <v>1881.25</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0</v>
+        <v>6906.5</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>2550</v>
+        <v>7411.905</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>526.5</v>
+        <v>28387.31</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>7920</v>
+        <v>25438.84</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>11116.5</v>
+        <v>9063.9</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>85829.70499999999</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>1580</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1" t="n">
+        <v>1580</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MEDEL LAB S.R.L.</t>
+          <t>M5 BIADESIVI SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F0001676</t>
+          <t>F003259</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>50.10.0503</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0001, 50.10.0303</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PAGAMENTO ANTICIPATO</t>
+        </is>
       </c>
       <c r="E36" s="1" t="n">
         <v>0</v>
@@ -2497,45 +4121,89 @@
         <v>0</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0</v>
+        <v>92.48</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>865.8</v>
+        <v>0</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>14026.2</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>2982</v>
+        <v>92.48</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>18729</v>
+        <v>0</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>184.96</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>METAL 3 SRL</t>
+          <t>MAGIC MP SPA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>F0000539</t>
+          <t>F0001361</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>54.10.0503</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0001</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BB RICEVIMENTO FATTURA</t>
+        </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>0</v>
@@ -2544,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>5.4047</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>0</v>
@@ -2559,42 +4227,86 @@
         <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>12910.61</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>14065.8898</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>5276.12</v>
+        <v>800</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>32358.02450000001</v>
+        <v>0</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MILANO BILANCE SRL</t>
+          <t>MANUPLAST SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F0002185</t>
+          <t>F0000666</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>50.10.0001</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>0</v>
+          <t>54.10.0502, 54.10.0503</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM + 5</t>
+        </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>0</v>
@@ -2609,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>0</v>
@@ -2624,29 +4336,77 @@
         <v>0</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>0</v>
+        <v>1397.5</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>1416</v>
+        <v>12398.92</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>14166.42</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>3193</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1" t="n">
+        <v>3193</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MORETTO P.A. SPA</t>
+          <t>MEDEL LAB S.R.L.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>F0001182</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="1" t="n">
-        <v>0</v>
+          <t>F0001676</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>50.10.0503, 50.20.0501, 54.10.0030</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM + 5</t>
+        </is>
       </c>
       <c r="E39" s="1" t="n">
         <v>0</v>
@@ -2655,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>793.35</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>0</v>
@@ -2682,32 +4442,80 @@
         <v>0</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>0</v>
+        <v>12734</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>793.35</v>
+        <v>855</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>13589</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>2733.5</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1" t="n">
+        <v>2733.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NINGBO BOOLONG PACKAGING CO. LTD</t>
+          <t>METAL 3 SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>F0002716</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="1" t="n">
-        <v>0</v>
+          <t>F0000539</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>50.10.0013, 54.10.0503</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BB30/60/90/120 GG FM+10</t>
+        </is>
       </c>
       <c r="E40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>0</v>
@@ -2716,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0</v>
+        <v>5.4047</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>0</v>
@@ -2725,48 +4533,92 @@
         <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>631.8667</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>0</v>
+        <v>4528.97</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>0</v>
+        <v>2670.7495</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>0</v>
+        <v>11109.63</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>3631.8667</v>
+        <v>57370.83</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>75785.58420000001</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>3958.81</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1" t="n">
+        <v>3958.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OLIVARES S.R.L.</t>
+          <t>MILANO BILANCE SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>F0001381</t>
+          <t>F0002185</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>52.10.0003</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>0</v>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>RIBA 60GG FM</t>
+        </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>240.03</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>100</v>
+        <v>1416</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>0</v>
@@ -2799,23 +4651,71 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>340.03</v>
+        <v>0</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>1416</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ORIGAMI</t>
+          <t>MORETTO P.A. SPA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>F0003148</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" s="1" t="n">
-        <v>0</v>
+          <t>F0001182</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RIBA 60GG FM + 5 GG</t>
+        </is>
       </c>
       <c r="E42" s="1" t="n">
         <v>0</v>
@@ -2827,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0</v>
+        <v>793.35</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>0</v>
@@ -2836,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>1246.2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>0</v>
@@ -2854,23 +4754,71 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>1246.2</v>
+        <v>0</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <v>793.35</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P.M.I SRL</t>
+          <t>NINGBO BOOLONG PACKAGING CO. LTD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>f03269</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" s="1" t="n">
-        <v>0</v>
+          <t>F0002716</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>25% ORDINE - 75% MERCE PRONTA</t>
+        </is>
       </c>
       <c r="E43" s="1" t="n">
         <v>0</v>
@@ -2900,32 +4848,80 @@
         <v>0</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>21740.8</v>
+        <v>0</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>22793.6</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>4600</v>
+        <v>3000</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>49134.4</v>
+        <v>0</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PADANA IMBALLAGGI S.R.L.</t>
+          <t>P.M.I SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>F0003050</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" s="1" t="n">
-        <v>0</v>
+          <t>f03269</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>50.10.0001</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E44" s="1" t="n">
         <v>0</v>
@@ -2952,42 +4948,86 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>995</v>
+        <v>0</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>0</v>
+        <v>6867</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>995</v>
+        <v>1680</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>8588.5</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PARISON S.N.C. DI BERTACCHINI ROBERTO E D'ANGELO F</t>
+          <t>PADANA IMBALLAGGI S.R.L.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>F0003149</t>
+          <t>F0003050</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>54.10.0504</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50% ANTICIPATO - SDO RIBA 30GGFM + 10</t>
+        </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>0</v>
@@ -3014,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>0</v>
+        <v>995</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>0</v>
@@ -3023,29 +5063,77 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>1200</v>
+        <v>0</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <v>995</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PGP GLASS PRIVATE LIMITED</t>
+          <t>PARISON S.N.C. DI BERTACCHINI ROBERTO E D'ANGELO F</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>F0005001</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" s="1" t="n">
-        <v>0</v>
+          <t>F0003149</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>54.10.0260</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RIBA 30/60/90/120GG FM</t>
+        </is>
       </c>
       <c r="E46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>10000</v>
+        <v>1200</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>0</v>
@@ -3078,27 +5166,71 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PUNTOLUBE SAS DI SILOTTO R. &amp; C.</t>
+          <t>PGP GLASS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>F0002170</t>
+          <t>F0005001</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>52.10.0202</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BB 60GG DATA CONSEGNA</t>
+        </is>
       </c>
       <c r="E47" s="1" t="n">
         <v>0</v>
@@ -3128,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>224.16</v>
+        <v>0</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>0</v>
@@ -3137,23 +5269,71 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>224.16</v>
+        <v>0</v>
+      </c>
+      <c r="R47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>152752.52</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>67817.09</v>
+      </c>
+      <c r="U47" s="1" t="n">
+        <v>56082.67</v>
+      </c>
+      <c r="V47" s="1" t="n">
+        <v>28035.07</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>81847.87</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1" t="n">
+        <v>386535.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SATIMAT</t>
+          <t>PUNTOLUBE SAS DI SILOTTO R. &amp; C.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>F0003061</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="1" t="n">
-        <v>0</v>
+          <t>F0002170</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>52.10.0202</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BB 60GG FM IL 5</t>
+        </is>
       </c>
       <c r="E48" s="1" t="n">
         <v>0</v>
@@ -3177,42 +5357,86 @@
         <v>0</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>86.8</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>1013.8</v>
+        <v>0</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>748.48</v>
+        <v>224.16</v>
       </c>
       <c r="P48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>1849.08</v>
+        <v>0</v>
+      </c>
+      <c r="R48" s="1" t="n">
+        <v>224.16</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SERILAMP DI PRESTINI ROBERTO</t>
+          <t>S.A. GERARD PARICHE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>F0002950</t>
+          <t>F0001331</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>52.10.0202</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BB 60GG FM</t>
+        </is>
       </c>
       <c r="E49" s="1" t="n">
         <v>0</v>
@@ -3233,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>0</v>
@@ -3248,30 +5472,74 @@
         <v>0</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>0</v>
+        <v>11438</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>228</v>
+        <v>0</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <v>11438</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SILGAN DISPENSING SYSTEMS MILANO S.R.L.</t>
+          <t>SATIMAT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>F0010247</t>
+          <t>F0003061</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>50.10.0504</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BB 60GG FM</t>
+        </is>
       </c>
       <c r="E50" s="1" t="n">
         <v>0</v>
@@ -3298,35 +5566,83 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>8278</v>
+        <v>86.8</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>1986.72</v>
+        <v>31</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>2155.1</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>12419.82</v>
+        <v>0</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="S50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOB SRL</t>
+          <t>SERILAMP DI PRESTINI ROBERTO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>F0007044</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="1" t="n">
-        <v>0</v>
+          <t>F0002950</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>54.10.0260</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BB RICEVIMENTO FATTURA</t>
+        </is>
       </c>
       <c r="E51" s="1" t="n">
         <v>0</v>
@@ -3350,13 +5666,13 @@
         <v>0</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>1156</v>
+        <v>0</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>0</v>
@@ -3365,23 +5681,71 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>1156</v>
+        <v>0</v>
+      </c>
+      <c r="R51" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TARGOS SAS</t>
+          <t>SILGAN DISPENSING SYSTEMS LACROST S.A.S.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>f0007036</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" s="1" t="n">
-        <v>270</v>
+          <t>F0003142</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BB 90GG DF FM</t>
+        </is>
       </c>
       <c r="E52" s="1" t="n">
         <v>0</v>
@@ -3420,27 +5784,71 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>270</v>
+        <v>0</v>
+      </c>
+      <c r="R52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TECHNICAPS PACKAGING S.A.</t>
+          <t>SILGAN DISPENSING SYSTEMS MILANO S.R.L.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>F0000042</t>
+          <t>F0010247</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>50.10.0706</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>0</v>
+          <t>50.10.0503, 50.10.0504</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BB 60/90 GG FM</t>
+        </is>
       </c>
       <c r="E53" s="1" t="n">
         <v>0</v>
@@ -3470,32 +5878,80 @@
         <v>0</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>43728</v>
+        <v>0</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>0</v>
+        <v>1986.72</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>43728</v>
+        <v>2155.1</v>
+      </c>
+      <c r="R53" s="1" t="n">
+        <v>4801.82</v>
+      </c>
+      <c r="S53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>11942.9</v>
+      </c>
+      <c r="U53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1" t="n">
+        <v>8278</v>
+      </c>
+      <c r="W53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1" t="n">
+        <v>8278</v>
+      </c>
+      <c r="Y53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1" t="n">
+        <v>8278</v>
+      </c>
+      <c r="AA53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1" t="n">
+        <v>36776.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UPG UNI-PRESIDENT GLASS INDUSTRIAL CO. LTD</t>
+          <t>SUGHERIFICIO GANDOLFI SPA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>F0002083</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="1" t="n">
-        <v>0</v>
+          <t>F0000017</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>50.10.0101, 50.10.0503, 50.20.0502</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BB 30/60 GG FM + 10</t>
+        </is>
       </c>
       <c r="E54" s="1" t="n">
         <v>0</v>
@@ -3519,42 +5975,86 @@
         <v>0</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>104260.61</v>
+        <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>37083.47</v>
+        <v>0</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>66420</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>0</v>
+        <v>6350</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>207764.08</v>
+        <v>0</v>
+      </c>
+      <c r="R54" s="1" t="n">
+        <v>6350</v>
+      </c>
+      <c r="S54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VERBAR SRL</t>
+          <t>TECHNICAPS PACKAGING S.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>F0005002</t>
+          <t>F0000042</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.10.0501</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BB 90GG DF FM</t>
+        </is>
       </c>
       <c r="E55" s="1" t="n">
         <v>0</v>
@@ -3566,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
@@ -3575,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="L55" s="1" t="n">
         <v>0</v>
@@ -3587,33 +6087,77 @@
         <v>0</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>0</v>
+        <v>26860.5</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>1900</v>
+        <v>23940</v>
+      </c>
+      <c r="R55" s="1" t="n">
+        <v>54628.5</v>
+      </c>
+      <c r="S55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VERNICIATURE BRESCIANE SRL</t>
+          <t>UPG UNI-PRESIDENT GLASS INDUSTRIAL CO. LTD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>F03270</t>
+          <t>F0002083</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.10.0501</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>0</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BB 60GG DATA CONSEGNA</t>
+        </is>
       </c>
       <c r="E56" s="1" t="n">
         <v>0</v>
@@ -3640,25 +6184,376 @@
         <v>0</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>26473.8</v>
+        <v>6687.36</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>18555.25</v>
+        <v>0</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>25564.76</v>
+        <v>38610</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>1020.95</v>
+        <v>78965.28</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>71614.76000000001</v>
+        <v>27810</v>
+      </c>
+      <c r="R56" s="1" t="n">
+        <v>152072.64</v>
+      </c>
+      <c r="S56" s="1" t="n">
+        <v>31415.04</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>12849</v>
+      </c>
+      <c r="U56" s="1" t="n">
+        <v>15177.46</v>
+      </c>
+      <c r="V56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1" t="n">
+        <v>59441.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VERBAR SRL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>F0005002</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>50.10.0013, 50.10.0501, 54.10.0501</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM + 5</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="S57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aggiornato al: 03/10/2025 14:48:24</t>
+          <t>VERNICIATURE BRESCIANE SRL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>F03270</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>54.10.0501</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BB 30/60/90 DF FM +10</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1" t="n">
+        <v>2141.16</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>11291.52</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>14950.2928</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>2465.36</v>
+      </c>
+      <c r="R58" s="1" t="n">
+        <v>30848.3328</v>
+      </c>
+      <c r="S58" s="1" t="n">
+        <v>7523.63</v>
+      </c>
+      <c r="T58" s="1" t="n">
+        <v>1829.5</v>
+      </c>
+      <c r="U58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="1" t="n">
+        <v>9353.130000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VETRERIE ITALIANE FORESTA S.R.L.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>F0003058</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BB 60GG FM IL 10</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>2225.8</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1" t="n">
+        <v>2225.8</v>
+      </c>
+      <c r="S59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aggiornato al: 05/11/2025 11:49:02</t>
         </is>
       </c>
     </row>
